--- a/0's and 1's.xlsx
+++ b/0's and 1's.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMAN MOHAMAD KAMAL\Desktop\CS-1\semester_2\Programming 2\GamEngine26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMAN MOHAMAD KAMAL\Desktop\GamEngine26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E045C009-86F6-4E59-884E-F14DF0666EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B3C96A-CA3F-458C-B70A-2816869C9C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCDEC367-906E-4865-B38C-EFA3132BCFFC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>Helen Hani</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>T3</t>
+  </si>
+  <si>
+    <t>مش محتاجه بجد كفايا اني خلصت مشكله git لوحدي من غير الذكاء(الاصطناعي)</t>
   </si>
 </sst>
 </file>
@@ -502,15 +505,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7669270A-725B-42BF-BB1B-6E1674507E36}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="53.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
@@ -530,31 +534,40 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2">
         <v>692500415</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1">
         <v>692500970</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1">
         <v>692500786</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -565,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -576,7 +589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -586,8 +599,11 @@
       <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -598,12 +614,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>692501147</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -622,6 +641,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="769f4189-d11d-41ab-8e98-2e8c15dffb45" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AC0CF407F347D247B7AE94492D3E7507" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f33cdb001b77c1b2568067b5ef4364d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="769f4189-d11d-41ab-8e98-2e8c15dffb45" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6bf403e3fa2abdf15e23668a513b6030" ns3:_="">
     <xsd:import namespace="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
@@ -771,14 +798,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="769f4189-d11d-41ab-8e98-2e8c15dffb45" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A1C7163-953F-4DCF-9FC4-72BB3EC3E91F}">
   <ds:schemaRefs>
@@ -788,6 +807,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DCC9CE-F447-45C9-9879-3F42F25484D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7815B5BE-455E-464A-A9AF-5A0F2109DB14}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -803,20 +838,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DCC9CE-F447-45C9-9879-3F42F25484D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/0's and 1's.xlsx
+++ b/0's and 1's.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMAN MOHAMAD KAMAL\Desktop\GamEngine26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B3C96A-CA3F-458C-B70A-2816869C9C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E877CE0-AFC2-4FA7-BA6E-A4E8703C4F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCDEC367-906E-4865-B38C-EFA3132BCFFC}"/>
+    <workbookView xWindow="3096" yWindow="1656" windowWidth="17280" windowHeight="8880" xr2:uid="{BCDEC367-906E-4865-B38C-EFA3132BCFFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
-    <t>Helen Hani</t>
-  </si>
-  <si>
     <t>Haneen Amr</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>Seif allah wael</t>
   </si>
   <si>
-    <t>Mohreal Khalaf</t>
-  </si>
-  <si>
     <t>team</t>
   </si>
   <si>
@@ -93,6 +87,12 @@
   </si>
   <si>
     <t>مش محتاجه بجد كفايا اني خلصت مشكله git لوحدي من غير الذكاء(الاصطناعي)</t>
+  </si>
+  <si>
+    <t>Mohraeel Khalaf</t>
+  </si>
+  <si>
+    <t>Helen Hany</t>
   </si>
 </sst>
 </file>
@@ -516,113 +516,113 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>692500415</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>692500970</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>692500786</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1">
         <v>692500794</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1">
         <v>692500796</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
         <v>692500811</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1">
         <v>692500815</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1">
         <v>692501147</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -641,14 +641,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="769f4189-d11d-41ab-8e98-2e8c15dffb45" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AC0CF407F347D247B7AE94492D3E7507" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f33cdb001b77c1b2568067b5ef4364d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="769f4189-d11d-41ab-8e98-2e8c15dffb45" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6bf403e3fa2abdf15e23668a513b6030" ns3:_="">
     <xsd:import namespace="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
@@ -798,6 +790,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="769f4189-d11d-41ab-8e98-2e8c15dffb45" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A1C7163-953F-4DCF-9FC4-72BB3EC3E91F}">
   <ds:schemaRefs>
@@ -807,22 +807,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DCC9CE-F447-45C9-9879-3F42F25484D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7815B5BE-455E-464A-A9AF-5A0F2109DB14}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -838,4 +822,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DCC9CE-F447-45C9-9879-3F42F25484D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="769f4189-d11d-41ab-8e98-2e8c15dffb45"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>